--- a/filehasil/materi_srq29/2026-08-16_laporan_hasil_akhir_Materi L.xlsx
+++ b/filehasil/materi_srq29/2026-08-16_laporan_hasil_akhir_Materi L.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>No.</t>
   </si>
@@ -56,10 +56,13 @@
     <t>POLRESTA PALEMBANG</t>
   </si>
   <si>
-    <t>1, 3, 4, 5, 6, 7, 13, 15, 18, 19, 20</t>
+    <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20</t>
   </si>
   <si>
     <t>22, 23, 24</t>
+  </si>
+  <si>
+    <t>25, 26</t>
   </si>
 </sst>
 </file>
@@ -407,10 +410,10 @@
     <col min="4" max="4" width="10" bestFit="true" customWidth="true" style="1"/>
     <col min="5" max="5" width="9" bestFit="true" customWidth="true" style="1"/>
     <col min="6" max="6" width="22" bestFit="true" customWidth="true" style="1"/>
-    <col min="7" max="7" width="43" bestFit="true" customWidth="true" style="1"/>
+    <col min="7" max="7" width="82" bestFit="true" customWidth="true" style="1"/>
     <col min="8" max="8" width="6" bestFit="true" customWidth="true" style="1"/>
     <col min="9" max="9" width="12" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="5" bestFit="true" customWidth="true" style="1"/>
+    <col min="10" max="10" width="8" bestFit="true" customWidth="true" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -471,8 +474,8 @@
       <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1">
-        <v>25</v>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
